--- a/static/files/patient_import_template.xlsx
+++ b/static/files/patient_import_template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adeba\Documents\isalu folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev3\clinic365\static\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>surname</t>
   </si>
@@ -74,12 +74,6 @@
     <t>insurance_policy_number</t>
   </si>
   <si>
-    <t>Jimoh</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
     <t>Married</t>
   </si>
   <si>
@@ -89,79 +83,28 @@
     <t>HMO</t>
   </si>
   <si>
-    <t>yt@gmail.com</t>
-  </si>
-  <si>
-    <t>Adekola James</t>
-  </si>
-  <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>Ufoma</t>
-  </si>
-  <si>
-    <t>Joy</t>
-  </si>
-  <si>
     <t>Female</t>
   </si>
   <si>
-    <t>Private</t>
-  </si>
-  <si>
-    <t>Family</t>
-  </si>
-  <si>
-    <t>tola@gmail.com</t>
-  </si>
-  <si>
-    <t>Folami Bright</t>
-  </si>
-  <si>
     <t>Mother</t>
   </si>
   <si>
     <t>Mrs. Oluchi</t>
   </si>
   <si>
-    <t>Mary</t>
-  </si>
-  <si>
-    <t>joyce@gmail.com</t>
-  </si>
-  <si>
-    <t>Kabiru</t>
-  </si>
-  <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Bolaji</t>
-  </si>
-  <si>
-    <t>Usman</t>
-  </si>
-  <si>
-    <t>Jolapo</t>
-  </si>
-  <si>
-    <t>Single</t>
-  </si>
-  <si>
     <t>AIICO MULTISHIELD</t>
   </si>
   <si>
-    <t>gcow@gmail.com</t>
-  </si>
-  <si>
-    <t>Folake</t>
-  </si>
-  <si>
-    <t>Salewa</t>
-  </si>
-  <si>
-    <t>Adebayo</t>
+    <t>Firepemi</t>
+  </si>
+  <si>
+    <t>Toyin</t>
+  </si>
+  <si>
+    <t>lola</t>
+  </si>
+  <si>
+    <t>great@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -169,7 +112,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="000"/>
+    <numFmt numFmtId="164" formatCode="000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -211,7 +154,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -494,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
@@ -566,198 +509,63 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D2" t="str">
-        <f>TEXT("1985-07-20","YYYY-MM-DD")</f>
-        <v>1985-07-20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="1">
-        <v>908787788</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2">
-        <v>55991</v>
-      </c>
-      <c r="M2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2">
-        <v>9087189909</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="str">
-        <f>TEXT("1985-07-21","YYYY-MM-DD")</f>
-        <v>1985-07-21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="1">
-        <v>908787088</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3">
-        <v>55190</v>
-      </c>
-      <c r="M3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O3">
-        <v>9087229909</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" t="str">
         <f>TEXT("1989-07-22","YYYY-MM-DD")</f>
         <v>1989-07-22</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1">
+        <v>978700111</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="1">
-        <v>908787988</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4">
-        <v>55390</v>
-      </c>
-      <c r="M4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O4">
-        <v>9087319909</v>
-      </c>
+      <c r="L2">
+        <v>88998</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2">
+        <v>2398989989</v>
+      </c>
+      <c r="P2">
+        <v>55789</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" t="str">
-        <f>TEXT("1989-07-22","YYYY-MM-DD")</f>
-        <v>1989-07-22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="1">
-        <v>908700988</v>
-      </c>
-      <c r="H5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L5">
-        <v>76765</v>
-      </c>
-      <c r="M5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N5" t="s">
-        <v>31</v>
-      </c>
-      <c r="O5">
-        <v>7798989989</v>
-      </c>
-      <c r="P5">
-        <v>78654</v>
-      </c>
+      <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="G6" s="1"/>
@@ -767,24 +575,12 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="G11" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1"/>
-    <hyperlink ref="K3" r:id="rId2"/>
-    <hyperlink ref="K4" r:id="rId3"/>
-    <hyperlink ref="K5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>